--- a/Starfront/文档/配置表/CardResource.xlsx
+++ b/Starfront/文档/配置表/CardResource.xlsx
@@ -1996,323 +1996,383 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr/>
-  <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
-  <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="46" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="19" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="17.25" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" ht="17.25" spans="1:11">
-      <c r="A2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" ht="17.25" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" ht="17.25" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" ht="17.25" spans="1:11">
-      <c r="A5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" s="4"/>
-    </row>
-    <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15" t="n">
-        <v>1001</v>
-      </c>
-      <c r="C6" s="15" t="str">
-        <v>采集站</v>
-      </c>
-      <c r="D6" s="15" t="str">
-        <v>固定卡；产出局内货币</v>
-      </c>
-      <c r="E6" s="15" t="str">
-        <v>优秀</v>
-      </c>
-      <c r="F6" s="15" t="str">
-        <v>远征殖民军</v>
-      </c>
-      <c r="G6" s="15" t="str">
-        <v>scene/battle/appearance/collector</v>
-      </c>
-      <c r="H6" s="15" t="str">
-        <v>建筑卡</v>
-      </c>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15" t="n">
-        <v>1002</v>
-      </c>
-      <c r="K6" s="15"/>
-    </row>
-    <row r="7" ht="27" customHeight="1">
-      <c r="A7" s="15"/>
-      <c r="B7" s="15" t="n">
-        <v>1101</v>
-      </c>
-      <c r="C7" s="15" t="str">
-        <v>优秀步兵</v>
-      </c>
-      <c r="D7" s="15" t="str">
-        <v>测试占位；共用步兵资源</v>
-      </c>
-      <c r="E7" s="15" t="str">
-        <v>优秀</v>
-      </c>
-      <c r="F7" s="15" t="str">
-        <v>远征殖民军</v>
-      </c>
-      <c r="G7" s="15" t="str">
-        <v>scene/battle/appearance/infantry_camp</v>
-      </c>
-      <c r="H7" s="15" t="str">
-        <v>兵种卡</v>
-      </c>
-      <c r="I7" s="15" t="n">
-        <v>1101</v>
-      </c>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-    </row>
-    <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15" t="n">
-        <v>1102</v>
-      </c>
-      <c r="C8" s="15" t="str">
-        <v>稀有步兵</v>
-      </c>
-      <c r="D8" s="15" t="str">
-        <v>测试占位；共用步兵资源</v>
-      </c>
-      <c r="E8" s="15" t="str">
-        <v>稀有</v>
-      </c>
-      <c r="F8" s="15" t="str">
-        <v>远征殖民军</v>
-      </c>
-      <c r="G8" s="15" t="str">
-        <v>scene/battle/appearance/infantry_camp</v>
-      </c>
-      <c r="H8" s="15" t="str">
-        <v>兵种卡</v>
-      </c>
-      <c r="I8" s="15" t="n">
-        <v>1102</v>
-      </c>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-    </row>
-    <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="15"/>
-      <c r="B9" s="15" t="n">
-        <v>1103</v>
-      </c>
-      <c r="C9" s="15" t="str">
-        <v>史诗步兵</v>
-      </c>
-      <c r="D9" s="15" t="str">
-        <v>测试占位；共用步兵资源</v>
-      </c>
-      <c r="E9" s="15" t="str">
-        <v>史诗</v>
-      </c>
-      <c r="F9" s="15" t="str">
-        <v>远征殖民军</v>
-      </c>
-      <c r="G9" s="15" t="str">
-        <v>scene/battle/appearance/infantry_camp</v>
-      </c>
-      <c r="H9" s="15" t="str">
-        <v>兵种卡</v>
-      </c>
-      <c r="I9" s="15" t="n">
-        <v>1103</v>
-      </c>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-    </row>
-    <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15" t="n">
-        <v>1104</v>
-      </c>
-      <c r="C10" s="15" t="str">
-        <v>传说步兵</v>
-      </c>
-      <c r="D10" s="15" t="str">
-        <v>测试占位；共用步兵资源</v>
-      </c>
-      <c r="E10" s="15" t="str">
-        <v>传说</v>
-      </c>
-      <c r="F10" s="15" t="str">
-        <v>远征殖民军</v>
-      </c>
-      <c r="G10" s="15" t="str">
-        <v>scene/battle/appearance/infantry_camp</v>
-      </c>
-      <c r="H10" s="15" t="str">
-        <v>兵种卡</v>
-      </c>
-      <c r="I10" s="15" t="n">
-        <v>1104</v>
-      </c>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="H3:J3"/>
-  </mergeCells>
-  <dataValidations count="3">
-    <dataValidation type="list" sqref="E6:E10000">
-      <formula1>"优秀,稀有,史诗,传说"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="F6:F10000">
-      <formula1>"远征殖民军,吞星虫族,辉晶族,自治智械"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="H6:H10000">
-      <formula1>"兵种卡,建筑卡"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing ns1:id="rId2"/>
-</worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <ns0:sheetPr/>
+  <ns0:dimension ref="A1:L11"/>
+  <ns0:sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
+  <ns0:cols>
+    <ns0:col min="1" max="1" width="8" customWidth="1"/>
+    <ns0:col min="2" max="2" width="10" customWidth="1"/>
+    <ns0:col min="3" max="3" width="16" customWidth="1"/>
+    <ns0:col min="4" max="4" width="30" customWidth="1"/>
+    <ns0:col min="5" max="5" width="12" customWidth="1"/>
+    <ns0:col min="6" max="6" width="20" customWidth="1"/>
+    <ns0:col min="7" max="7" width="46" customWidth="1"/>
+    <ns0:col min="8" max="8" width="16" customWidth="1"/>
+    <ns0:col min="9" max="9" width="12" customWidth="1"/>
+    <ns0:col min="10" max="10" width="12" customWidth="1"/>
+    <ns0:col min="11" max="11" width="19" customWidth="1"/>
+    <ns0:col min="12" max="12" width="32" customWidth="1"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1" ht="17.25" spans="1:11">
+      <ns0:c r="A1" s="1" t="s">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="B1" s="2" t="s">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="C1" s="2" t="s">
+        <ns0:v>2</ns0:v>
+      </ns0:c>
+      <ns0:c r="D1" s="2" t="s">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+      <ns0:c r="E1" s="2" t="s">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
+      <ns0:c r="F1" s="2" t="s">
+        <ns0:v>5</ns0:v>
+      </ns0:c>
+      <ns0:c r="G1" s="2" t="s">
+        <ns0:v>6</ns0:v>
+      </ns0:c>
+      <ns0:c r="H1" s="2" t="s">
+        <ns0:v>7</ns0:v>
+      </ns0:c>
+      <ns0:c r="I1" s="2"/>
+      <ns0:c r="J1" s="2"/>
+      <ns0:c r="K1" s="2" t="s">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
+      <ns0:c r="L1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>unlockWeight</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="2" ht="17.25" spans="1:11">
+      <ns0:c r="A2" s="3" t="s">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="B2" s="4" t="s">
+        <ns0:v>10</ns0:v>
+      </ns0:c>
+      <ns0:c r="C2" s="4" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="D2" s="4" t="s">
+        <ns0:v>12</ns0:v>
+      </ns0:c>
+      <ns0:c r="E2" s="4" t="s">
+        <ns0:v>13</ns0:v>
+      </ns0:c>
+      <ns0:c r="F2" s="4" t="s">
+        <ns0:v>14</ns0:v>
+      </ns0:c>
+      <ns0:c r="G2" s="4" t="s">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="H2" s="4" t="s">
+        <ns0:v>16</ns0:v>
+      </ns0:c>
+      <ns0:c r="I2" s="4"/>
+      <ns0:c r="J2" s="4"/>
+      <ns0:c r="K2" s="4" t="s">
+        <ns0:v>17</ns0:v>
+      </ns0:c>
+      <ns0:c r="L2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>同品质兵种卡解锁权重（正整数）</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="3" ht="17.25" spans="1:11">
+      <ns0:c r="A3" s="1" t="s">
+        <ns0:v>18</ns0:v>
+      </ns0:c>
+      <ns0:c r="B3" s="2" t="s">
+        <ns0:v>19</ns0:v>
+      </ns0:c>
+      <ns0:c r="C3" s="2" t="s">
+        <ns0:v>20</ns0:v>
+      </ns0:c>
+      <ns0:c r="D3" s="2" t="s">
+        <ns0:v>20</ns0:v>
+      </ns0:c>
+      <ns0:c r="E3" s="2" t="s">
+        <ns0:v>21</ns0:v>
+      </ns0:c>
+      <ns0:c r="F3" s="2" t="s">
+        <ns0:v>22</ns0:v>
+      </ns0:c>
+      <ns0:c r="G3" s="2" t="s">
+        <ns0:v>20</ns0:v>
+      </ns0:c>
+      <ns0:c r="H3" s="2" t="s">
+        <ns0:v>23</ns0:v>
+      </ns0:c>
+      <ns0:c r="I3" s="2"/>
+      <ns0:c r="J3" s="2"/>
+      <ns0:c r="K3" s="2" t="s">
+        <ns0:v>19</ns0:v>
+      </ns0:c>
+      <ns0:c r="L3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>int</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="4" ht="17.25" spans="1:11">
+      <ns0:c r="A4" s="1" t="s">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="B4" s="2"/>
+      <ns0:c r="C4" s="2"/>
+      <ns0:c r="D4" s="2"/>
+      <ns0:c r="E4" s="2"/>
+      <ns0:c r="F4" s="2"/>
+      <ns0:c r="G4" s="2"/>
+      <ns0:c r="H4" s="2" t="s">
+        <ns0:v>24</ns0:v>
+      </ns0:c>
+      <ns0:c r="I4" s="2" t="s">
+        <ns0:v>25</ns0:v>
+      </ns0:c>
+      <ns0:c r="J4" s="2" t="s">
+        <ns0:v>26</ns0:v>
+      </ns0:c>
+      <ns0:c r="K4" s="2"/>
+    </ns0:row>
+    <ns0:row r="5" ht="17.25" spans="1:11">
+      <ns0:c r="A5" s="3" t="s">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="B5" s="4"/>
+      <ns0:c r="C5" s="4"/>
+      <ns0:c r="D5" s="4"/>
+      <ns0:c r="E5" s="4"/>
+      <ns0:c r="F5" s="4"/>
+      <ns0:c r="G5" s="4"/>
+      <ns0:c r="H5" s="4" t="s">
+        <ns0:v>27</ns0:v>
+      </ns0:c>
+      <ns0:c r="I5" s="4" t="s">
+        <ns0:v>28</ns0:v>
+      </ns0:c>
+      <ns0:c r="J5" s="4" t="s">
+        <ns0:v>29</ns0:v>
+      </ns0:c>
+      <ns0:c r="K5" s="4"/>
+    </ns0:row>
+    <ns0:row r="6" ht="27" customHeight="1">
+      <ns0:c r="A6" s="15"/>
+      <ns0:c r="B6" s="15" t="n">
+        <ns0:v>1001</ns0:v>
+      </ns0:c>
+      <ns0:c r="C6" s="15" t="str">
+        <ns0:v>采集站</ns0:v>
+      </ns0:c>
+      <ns0:c r="D6" s="15" t="str">
+        <ns0:v>固定卡；产出局内货币</ns0:v>
+      </ns0:c>
+      <ns0:c r="E6" s="15" t="str">
+        <ns0:v>优秀</ns0:v>
+      </ns0:c>
+      <ns0:c r="F6" s="15" t="str">
+        <ns0:v>远征殖民军</ns0:v>
+      </ns0:c>
+      <ns0:c r="G6" s="15" t="str">
+        <ns0:v>scene/battle/appearance/collector</ns0:v>
+      </ns0:c>
+      <ns0:c r="H6" s="15" t="str">
+        <ns0:v>建筑卡</ns0:v>
+      </ns0:c>
+      <ns0:c r="I6" s="15"/>
+      <ns0:c r="J6" s="15" t="n">
+        <ns0:v>1002</ns0:v>
+      </ns0:c>
+      <ns0:c r="K6" s="15"/>
+      <ns0:c r="L6">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="7" ht="27" customHeight="1">
+      <ns0:c r="A7" s="15"/>
+      <ns0:c r="B7" s="15" t="n">
+        <ns0:v>1101</ns0:v>
+      </ns0:c>
+      <ns0:c r="C7" s="15" t="str">
+        <ns0:v>优秀步兵</ns0:v>
+      </ns0:c>
+      <ns0:c r="D7" s="15" t="str">
+        <ns0:v>测试占位；共用步兵资源</ns0:v>
+      </ns0:c>
+      <ns0:c r="E7" s="15" t="str">
+        <ns0:v>优秀</ns0:v>
+      </ns0:c>
+      <ns0:c r="F7" s="15" t="str">
+        <ns0:v>远征殖民军</ns0:v>
+      </ns0:c>
+      <ns0:c r="G7" s="15" t="str">
+        <ns0:v>scene/battle/appearance/infantry_camp</ns0:v>
+      </ns0:c>
+      <ns0:c r="H7" s="15" t="str">
+        <ns0:v>兵种卡</ns0:v>
+      </ns0:c>
+      <ns0:c r="I7" s="15" t="n">
+        <ns0:v>1101</ns0:v>
+      </ns0:c>
+      <ns0:c r="J7" s="15"/>
+      <ns0:c r="K7" s="15"/>
+      <ns0:c r="L7">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="8" ht="27" customHeight="1">
+      <ns0:c r="A8" s="15"/>
+      <ns0:c r="B8" s="15" t="n">
+        <ns0:v>1102</ns0:v>
+      </ns0:c>
+      <ns0:c r="C8" s="15" t="str">
+        <ns0:v>稀有步兵</ns0:v>
+      </ns0:c>
+      <ns0:c r="D8" s="15" t="str">
+        <ns0:v>测试占位；共用步兵资源</ns0:v>
+      </ns0:c>
+      <ns0:c r="E8" s="15" t="str">
+        <ns0:v>稀有</ns0:v>
+      </ns0:c>
+      <ns0:c r="F8" s="15" t="str">
+        <ns0:v>远征殖民军</ns0:v>
+      </ns0:c>
+      <ns0:c r="G8" s="15" t="str">
+        <ns0:v>scene/battle/appearance/infantry_camp</ns0:v>
+      </ns0:c>
+      <ns0:c r="H8" s="15" t="str">
+        <ns0:v>兵种卡</ns0:v>
+      </ns0:c>
+      <ns0:c r="I8" s="15" t="n">
+        <ns0:v>1102</ns0:v>
+      </ns0:c>
+      <ns0:c r="J8" s="15"/>
+      <ns0:c r="K8" s="15"/>
+      <ns0:c r="L8">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="9" ht="27" customHeight="1">
+      <ns0:c r="A9" s="15"/>
+      <ns0:c r="B9" s="15" t="n">
+        <ns0:v>1103</ns0:v>
+      </ns0:c>
+      <ns0:c r="C9" s="15" t="str">
+        <ns0:v>史诗步兵</ns0:v>
+      </ns0:c>
+      <ns0:c r="D9" s="15" t="str">
+        <ns0:v>测试占位；共用步兵资源</ns0:v>
+      </ns0:c>
+      <ns0:c r="E9" s="15" t="str">
+        <ns0:v>史诗</ns0:v>
+      </ns0:c>
+      <ns0:c r="F9" s="15" t="str">
+        <ns0:v>远征殖民军</ns0:v>
+      </ns0:c>
+      <ns0:c r="G9" s="15" t="str">
+        <ns0:v>scene/battle/appearance/infantry_camp</ns0:v>
+      </ns0:c>
+      <ns0:c r="H9" s="15" t="str">
+        <ns0:v>兵种卡</ns0:v>
+      </ns0:c>
+      <ns0:c r="I9" s="15" t="n">
+        <ns0:v>1103</ns0:v>
+      </ns0:c>
+      <ns0:c r="J9" s="15"/>
+      <ns0:c r="K9" s="15"/>
+      <ns0:c r="L9">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="10" ht="27" customHeight="1">
+      <ns0:c r="A10" s="15"/>
+      <ns0:c r="B10" s="15" t="n">
+        <ns0:v>1104</ns0:v>
+      </ns0:c>
+      <ns0:c r="C10" s="15" t="str">
+        <ns0:v>传说步兵</ns0:v>
+      </ns0:c>
+      <ns0:c r="D10" s="15" t="str">
+        <ns0:v>测试占位；共用步兵资源</ns0:v>
+      </ns0:c>
+      <ns0:c r="E10" s="15" t="str">
+        <ns0:v>传说</ns0:v>
+      </ns0:c>
+      <ns0:c r="F10" s="15" t="str">
+        <ns0:v>远征殖民军</ns0:v>
+      </ns0:c>
+      <ns0:c r="G10" s="15" t="str">
+        <ns0:v>scene/battle/appearance/infantry_camp</ns0:v>
+      </ns0:c>
+      <ns0:c r="H10" s="15" t="str">
+        <ns0:v>兵种卡</ns0:v>
+      </ns0:c>
+      <ns0:c r="I10" s="15" t="n">
+        <ns0:v>1104</ns0:v>
+      </ns0:c>
+      <ns0:c r="J10" s="15"/>
+      <ns0:c r="K10" s="15"/>
+      <ns0:c r="L10">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="11" ht="25" customHeight="1">
+      <ns0:c r="B11" t="n" s="15">
+        <ns0:v>1201</ns0:v>
+      </ns0:c>
+      <ns0:c r="C11" t="str" s="15">
+        <ns0:v>女妖战机</ns0:v>
+      </ns0:c>
+      <ns0:c r="D11" t="str" s="15">
+        <ns0:v>飞行对地单位，由机场生产；卡面暂用机场占位</ns0:v>
+      </ns0:c>
+      <ns0:c r="E11" t="str" s="15">
+        <ns0:v>稀有</ns0:v>
+      </ns0:c>
+      <ns0:c r="F11" t="str" s="15">
+        <ns0:v>远征殖民军</ns0:v>
+      </ns0:c>
+      <ns0:c r="G11" t="str" s="15">
+        <ns0:v>scene/battle/appearance/airport</ns0:v>
+      </ns0:c>
+      <ns0:c r="H11" t="str" s="15">
+        <ns0:v>兵种卡</ns0:v>
+      </ns0:c>
+      <ns0:c r="I11" t="n" s="15">
+        <ns0:v>1201</ns0:v>
+      </ns0:c>
+      <ns0:c r="L11">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:mergeCells count="3">
+    <ns0:mergeCell ref="H1:J1"/>
+    <ns0:mergeCell ref="H2:J2"/>
+    <ns0:mergeCell ref="H3:J3"/>
+  </ns0:mergeCells>
+  <ns0:dataValidations count="3">
+    <ns0:dataValidation type="list" sqref="E6:E10000">
+      <ns0:formula1>"优秀,稀有,史诗,传说"</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" sqref="F6:F10000">
+      <ns0:formula1>"远征殖民军,吞星虫族,辉晶族,自治智械"</ns0:formula1>
+    </ns0:dataValidation>
+    <ns0:dataValidation type="list" sqref="H6:H10000">
+      <ns0:formula1>"兵种卡,建筑卡"</ns0:formula1>
+    </ns0:dataValidation>
+  </ns0:dataValidations>
+  <ns0:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ns0:headerFooter/>
+  <ns0:legacyDrawing ns1:id="rId2"/>
+</ns0:worksheet>
 </file>